--- a/data/sample_tracking.xlsx
+++ b/data/sample_tracking.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Manual Entries" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Manual Entry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,51 +417,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Timestamp</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Quantity of Santa Pants Cocktail "Garnishes" Requested (150 per order)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Account Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Address 2</t>
+          <t>Shipping Address</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>City &amp; State</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ZIP code</t>
+          <t>Contact Phone Number</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Kit quantity</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>Preferred Delivery Window</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Account Instagram Handle (for Social Promotions)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
@@ -471,33 +481,33 @@
       <c r="A2" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Avery Example</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Example Tavern</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>100 Sample St</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>43004</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>100000000001</v>
       </c>
     </row>
@@ -505,38 +515,38 @@
       <c r="A3" s="1" t="n">
         <v>46302</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Jordan Placeholder</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22 Test Ave</t>
+          <t>Placeholder Lounge</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Suite 4</t>
+          <t>22 Test Ave Suite 4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>80014</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>@placeholderlounge</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>1000 0000 0003</t>
         </is>
@@ -546,33 +556,33 @@
       <c r="A4" s="1" t="n">
         <v>46303</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Riley Demo</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Demo Bar &amp; Grill</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>9 Mock Rd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>73301</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>100000000006</v>
       </c>
     </row>
@@ -580,33 +590,33 @@
       <c r="A5" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Casey Fiction</t>
-        </is>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Fiction Pub</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>450 Fake Blvd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>33601</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>100000000007</v>
       </c>
     </row>
@@ -614,69 +624,64 @@
       <c r="A6" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Morgan Sample</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7 Pretend Ln</t>
+          <t>Sample Spirits Co</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apt 2B</t>
+          <t>7 Pretend Ln Apt 2B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>97035</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Quinn Invented</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Invented Inn</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>31 Imaginary Way</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raleigh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>27601</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Week of November 2 (first available)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>1.00000E+11</t>
         </is>
@@ -693,155 +698,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Address 2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ZIP code</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Kit quantity</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Kit Quantity</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Tracking</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Holiday 26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Taylor Madeup</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Madeup Taproom</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>8 Nowhere Ct</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Boise</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>83702</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>100000000002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Holiday 26</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Drew Synthetic</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Synthetic Saloon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>64 Specimen Dr</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Omaha</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>68102</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>100000000009</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Holiday 26</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>46306</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sam Notreal</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Notreal Brewhouse</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>12 Hypothetical Pl</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Madison</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>53703</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>999999999999</v>
       </c>
     </row>
